--- a/PlantillaML.xlsx
+++ b/PlantillaML.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manuel Rodriguez\source\repos\Unidades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548AC32A-9BAD-48EB-A3AB-A8336FF3A9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CC8A44-386F-4C4B-AB84-C2CC5B9178AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2760" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-2715" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>s</t>
   </si>
@@ -49,6 +49,18 @@
   </si>
   <si>
     <t>COORDENADAS</t>
+  </si>
+  <si>
+    <t>ID ROSTERING</t>
+  </si>
+  <si>
+    <t>ORIGEN</t>
+  </si>
+  <si>
+    <t>DESTINO</t>
+  </si>
+  <si>
+    <t>PLACAS</t>
   </si>
 </sst>
 </file>
@@ -101,7 +113,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
       <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -134,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -143,17 +155,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -227,17 +228,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -279,6 +269,19 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -288,58 +291,60 @@
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,401 +625,533 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="22" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" style="22" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="22" customWidth="1"/>
-    <col min="4" max="7" width="11.42578125" style="22"/>
-    <col min="8" max="8" width="20.140625" style="22" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="22" customWidth="1"/>
-    <col min="10" max="10" width="27" style="24" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="17" customWidth="1"/>
+    <col min="4" max="5" width="18.42578125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="17" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="17" customWidth="1"/>
+    <col min="8" max="11" width="11.42578125" style="17"/>
+    <col min="12" max="12" width="20.140625" style="17" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="17" customWidth="1"/>
+    <col min="14" max="14" width="27" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="4" t="s">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="5" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="18" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="15"/>
-    </row>
-    <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="J3" s="7"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="5"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="5"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="12"/>
+    </row>
+    <row r="7" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="E7" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="G7" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="16" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="23"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="23"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
-      <c r="B10" s="25"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="23"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="23"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="23"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="23"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="23"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="23"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="23"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="23"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="23"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="23"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="23"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="23"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="23"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="23"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="23"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="23"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="23"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="23"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="23"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="23"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="23"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="23"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="23"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="23"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="23"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="23"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="23"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="23"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="23"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="23"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="23"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="23"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="23"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="23"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="23"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="23"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="23"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="23"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="23"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="23"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="23"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="23"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="23"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="23"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="23"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="23"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="23"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="23"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="23"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="23"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="23"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="23"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="23"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="23"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="23"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="23"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="23"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="23"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="23"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="23"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="23"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="23"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="23"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="23"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="23"/>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="20"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+    </row>
+    <row r="25" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+    </row>
+    <row r="34" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+    </row>
+    <row r="35" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+    </row>
+    <row r="36" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+    </row>
+    <row r="37" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+    </row>
+    <row r="39" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+    </row>
+    <row r="40" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+    </row>
+    <row r="41" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+    </row>
+    <row r="42" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+    </row>
+    <row r="43" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+    </row>
+    <row r="44" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+    </row>
+    <row r="45" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+    </row>
+    <row r="46" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+    </row>
+    <row r="47" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+    </row>
+    <row r="48" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+    </row>
+    <row r="49" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+    </row>
+    <row r="50" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+    </row>
+    <row r="51" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+    </row>
+    <row r="52" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+    </row>
+    <row r="53" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+    </row>
+    <row r="54" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+    </row>
+    <row r="55" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+    </row>
+    <row r="56" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+    </row>
+    <row r="57" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+    </row>
+    <row r="58" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+    </row>
+    <row r="59" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+    </row>
+    <row r="60" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+    </row>
+    <row r="61" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+    </row>
+    <row r="62" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+    </row>
+    <row r="63" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+    </row>
+    <row r="64" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+    </row>
+    <row r="65" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+    </row>
+    <row r="66" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+    </row>
+    <row r="67" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+    </row>
+    <row r="68" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+    </row>
+    <row r="69" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+    </row>
+    <row r="70" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+    </row>
+    <row r="71" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+    </row>
+    <row r="72" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+    </row>
+    <row r="73" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+    </row>
+    <row r="74" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+    </row>
+    <row r="75" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+    </row>
+    <row r="76" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+    </row>
+    <row r="77" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+    </row>
+    <row r="78" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+    </row>
+    <row r="79" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+    </row>
+    <row r="80" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+    </row>
+    <row r="81" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+    </row>
+    <row r="82" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+    </row>
+    <row r="83" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+    </row>
+    <row r="84" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+    </row>
+    <row r="85" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+    </row>
+    <row r="86" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+    </row>
+    <row r="87" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+    </row>
+    <row r="88" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+    </row>
+    <row r="89" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+    </row>
+    <row r="90" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D90" s="18"/>
+      <c r="E90" s="18"/>
+    </row>
+    <row r="91" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D91" s="18"/>
+      <c r="E91" s="18"/>
+    </row>
+    <row r="92" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+    </row>
+    <row r="93" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+    </row>
+    <row r="94" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D94" s="18"/>
+      <c r="E94" s="18"/>
+    </row>
+    <row r="95" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D95" s="18"/>
+      <c r="E95" s="18"/>
+    </row>
+    <row r="96" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D96" s="18"/>
+      <c r="E96" s="18"/>
+    </row>
+    <row r="97" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D97" s="18"/>
+      <c r="E97" s="18"/>
+    </row>
+    <row r="98" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D98" s="18"/>
+      <c r="E98" s="18"/>
+    </row>
+    <row r="99" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D99" s="18"/>
+      <c r="E99" s="18"/>
+    </row>
+    <row r="100" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D100" s="18"/>
+      <c r="E100" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="G7:M7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PlantillaML.xlsx
+++ b/PlantillaML.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manuel Rodriguez\source\repos\Unidades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manuel Rodriguez\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CC8A44-386F-4C4B-AB84-C2CC5B9178AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43DC0D1-2BE4-4B09-B46C-B360947790E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-2715" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10005" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>s</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>TOTAL DE UNIDADES</t>
   </si>
@@ -49,18 +46,6 @@
   </si>
   <si>
     <t>COORDENADAS</t>
-  </si>
-  <si>
-    <t>ID ROSTERING</t>
-  </si>
-  <si>
-    <t>ORIGEN</t>
-  </si>
-  <si>
-    <t>DESTINO</t>
-  </si>
-  <si>
-    <t>PLACAS</t>
   </si>
 </sst>
 </file>
@@ -184,19 +169,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -215,19 +187,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -248,19 +207,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -279,6 +225,43 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -288,63 +271,69 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,531 +617,503 @@
   <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.140625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="17" customWidth="1"/>
-    <col min="4" max="5" width="18.42578125" style="17" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="17" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" style="17" customWidth="1"/>
-    <col min="8" max="11" width="11.42578125" style="17"/>
-    <col min="12" max="12" width="20.140625" style="17" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="17" customWidth="1"/>
-    <col min="14" max="14" width="27" style="19" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="18"/>
+    <col min="12" max="12" width="20.140625" style="18" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" style="18" customWidth="1"/>
+    <col min="14" max="14" width="27" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="3" t="s">
+      <c r="J1" s="23"/>
+      <c r="L1" s="19"/>
+      <c r="N1" s="20"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="24"/>
+      <c r="N2" s="21"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="I3" s="25" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="13"/>
-      <c r="N2" s="5"/>
-    </row>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14" t="s">
+      <c r="J3" s="24"/>
+      <c r="N3" s="21"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="24"/>
+      <c r="N4" s="21"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="27"/>
+      <c r="N5" s="21"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+    </row>
+    <row r="7" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="5"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="5"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="5"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="12"/>
-    </row>
-    <row r="7" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="23" t="s">
+      <c r="C7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="23" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="20"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="L13" s="29"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
     </row>
     <row r="37" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
     </row>
     <row r="40" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
     </row>
     <row r="41" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
     </row>
     <row r="42" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
     </row>
     <row r="43" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
     </row>
     <row r="44" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
     </row>
     <row r="45" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
     </row>
     <row r="46" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
     </row>
     <row r="47" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
     </row>
     <row r="48" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
     </row>
     <row r="50" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
     </row>
     <row r="51" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
     </row>
     <row r="52" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
     </row>
     <row r="53" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
     </row>
     <row r="54" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
     </row>
     <row r="55" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
     </row>
     <row r="56" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
     </row>
     <row r="57" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
     </row>
     <row r="58" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
     </row>
     <row r="59" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
     </row>
     <row r="60" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
     </row>
     <row r="61" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
     </row>
     <row r="62" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
     </row>
     <row r="63" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
     </row>
     <row r="64" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
     </row>
     <row r="65" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
     </row>
     <row r="66" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
     </row>
     <row r="67" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
     </row>
     <row r="68" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
     </row>
     <row r="69" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
     </row>
     <row r="70" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
     </row>
     <row r="71" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
     </row>
     <row r="72" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
     </row>
     <row r="73" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
     </row>
     <row r="74" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
     </row>
     <row r="75" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
     </row>
     <row r="76" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
     </row>
     <row r="77" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
     </row>
     <row r="78" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
     </row>
     <row r="79" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
     </row>
     <row r="80" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
     </row>
     <row r="81" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
     </row>
     <row r="82" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
     </row>
     <row r="83" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
     </row>
     <row r="84" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D84" s="18"/>
-      <c r="E84" s="18"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="10"/>
     </row>
     <row r="85" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
     </row>
     <row r="86" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D86" s="18"/>
-      <c r="E86" s="18"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="10"/>
     </row>
     <row r="87" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="10"/>
     </row>
     <row r="88" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
     </row>
     <row r="89" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
     </row>
     <row r="90" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D90" s="18"/>
-      <c r="E90" s="18"/>
+      <c r="D90" s="10"/>
+      <c r="E90" s="10"/>
     </row>
     <row r="91" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
+      <c r="D91" s="10"/>
+      <c r="E91" s="10"/>
     </row>
     <row r="92" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D92" s="18"/>
-      <c r="E92" s="18"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
     </row>
     <row r="93" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
+      <c r="D93" s="10"/>
+      <c r="E93" s="10"/>
     </row>
     <row r="94" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D94" s="18"/>
-      <c r="E94" s="18"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="10"/>
     </row>
     <row r="95" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D95" s="18"/>
-      <c r="E95" s="18"/>
+      <c r="D95" s="10"/>
+      <c r="E95" s="10"/>
     </row>
     <row r="96" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D96" s="18"/>
-      <c r="E96" s="18"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10"/>
     </row>
     <row r="97" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
+      <c r="D97" s="10"/>
+      <c r="E97" s="10"/>
     </row>
     <row r="98" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D98" s="18"/>
-      <c r="E98" s="18"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
     </row>
     <row r="99" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D99" s="18"/>
-      <c r="E99" s="18"/>
+      <c r="D99" s="10"/>
+      <c r="E99" s="10"/>
     </row>
     <row r="100" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D100" s="18"/>
-      <c r="E100" s="18"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G7:M7"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>